--- a/outputs/M6b_tourism_robustness_from_M4_regression_detail.xlsx
+++ b/outputs/M6b_tourism_robustness_from_M4_regression_detail.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>variable</t>
   </si>
@@ -40,19 +40,22 @@
     <t>Intercept</t>
   </si>
   <si>
+    <t>inflation_gdp_deflator_pct</t>
+  </si>
+  <si>
+    <t>trade_pct_gdp</t>
+  </si>
+  <si>
+    <t>ln_gdppc</t>
+  </si>
+  <si>
+    <t>xr_dep_pct</t>
+  </si>
+  <si>
     <t>broad_money_pct_gdp</t>
   </si>
   <si>
     <t>real_interest_rate_pct</t>
-  </si>
-  <si>
-    <t>trade_pct_gdp</t>
-  </si>
-  <si>
-    <t>ln_gdppc</t>
-  </si>
-  <si>
-    <t>xr_dep_pct</t>
   </si>
   <si>
     <t>ln_tourism_arrivals</t>
@@ -413,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -444,22 +447,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>33.69869179754293</v>
+        <v>23.55391278391144</v>
       </c>
       <c r="C2">
-        <v>29.85249397879979</v>
+        <v>18.85268548824094</v>
       </c>
       <c r="D2">
-        <v>1.128840083561346</v>
+        <v>1.249366452254391</v>
       </c>
       <c r="E2">
-        <v>0.2628191508509543</v>
+        <v>0.2157526692228244</v>
       </c>
       <c r="F2">
-        <v>-25.84023007270123</v>
+        <v>-14.05616569331358</v>
       </c>
       <c r="G2">
-        <v>93.2376136677871</v>
+        <v>61.16399126113646</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -467,22 +470,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>0.110297695465071</v>
+        <v>-0.5806825349518495</v>
       </c>
       <c r="C3">
-        <v>0.06924811539052118</v>
+        <v>0.1331786876284242</v>
       </c>
       <c r="D3">
-        <v>1.59278985201334</v>
+        <v>-4.360176130973639</v>
       </c>
       <c r="E3">
-        <v>0.1157133098426304</v>
+        <v>4.441200269100776E-05</v>
       </c>
       <c r="F3">
-        <v>-0.02781331578999793</v>
+        <v>-0.8463667472261733</v>
       </c>
       <c r="G3">
-        <v>0.2484087067201398</v>
+        <v>-0.3149983226775256</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -490,22 +493,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>-0.08418377674038259</v>
+        <v>-0.03862170649776309</v>
       </c>
       <c r="C4">
-        <v>0.08913305212719273</v>
+        <v>0.01379335142416218</v>
       </c>
       <c r="D4">
-        <v>-0.9444731750041776</v>
+        <v>-2.800023381562543</v>
       </c>
       <c r="E4">
-        <v>0.3481765414838782</v>
+        <v>0.006622196106624401</v>
       </c>
       <c r="F4">
-        <v>-0.2619540437882915</v>
+        <v>-0.06613868968035831</v>
       </c>
       <c r="G4">
-        <v>0.09358649030752626</v>
+        <v>-0.01110472331516787</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -513,22 +516,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>-0.04073008773644147</v>
+        <v>-0.6570380213946319</v>
       </c>
       <c r="C5">
-        <v>0.02811988247030426</v>
+        <v>1.702042261346384</v>
       </c>
       <c r="D5">
-        <v>-1.44844445133987</v>
+        <v>-0.3860292052177884</v>
       </c>
       <c r="E5">
-        <v>0.1519574950740072</v>
+        <v>0.7006627693654872</v>
       </c>
       <c r="F5">
-        <v>-0.0968134249138603</v>
+        <v>-4.052519426986354</v>
       </c>
       <c r="G5">
-        <v>0.01535324944097736</v>
+        <v>2.738443384197091</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -536,22 +539,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>-1.814074350110893</v>
+        <v>0.1563052481550004</v>
       </c>
       <c r="C6">
-        <v>2.824438218966535</v>
+        <v>0.06635874296351779</v>
       </c>
       <c r="D6">
-        <v>-0.6422779361676618</v>
+        <v>2.355458243700197</v>
       </c>
       <c r="E6">
-        <v>0.5227907364580253</v>
+        <v>0.02134841171578494</v>
       </c>
       <c r="F6">
-        <v>-7.447238753922662</v>
+        <v>0.02392317812765093</v>
       </c>
       <c r="G6">
-        <v>3.819090053700876</v>
+        <v>0.2886873181823499</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -559,22 +562,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.04356327100893288</v>
+        <v>0.0397526641451743</v>
       </c>
       <c r="C7">
-        <v>0.05232145160743972</v>
+        <v>0.05419130707645709</v>
       </c>
       <c r="D7">
-        <v>0.8326082260825216</v>
+        <v>0.7335616409674028</v>
       </c>
       <c r="E7">
-        <v>0.4078974307228855</v>
+        <v>0.4657011376959139</v>
       </c>
       <c r="F7">
-        <v>-0.06078857381868508</v>
+        <v>-0.06835603544567218</v>
       </c>
       <c r="G7">
-        <v>0.1479151158365508</v>
+        <v>0.1478613637360208</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -582,22 +585,45 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>-1.155011538502882</v>
+        <v>-0.6444652332392524</v>
       </c>
       <c r="C8">
-        <v>1.010565872011123</v>
+        <v>0.2051471970746173</v>
       </c>
       <c r="D8">
-        <v>-1.142935429042639</v>
+        <v>-3.141477156058067</v>
       </c>
       <c r="E8">
-        <v>0.2569594098961931</v>
+        <v>0.00247621923669894</v>
       </c>
       <c r="F8">
-        <v>-3.170521617531277</v>
+        <v>-1.053722693465361</v>
       </c>
       <c r="G8">
-        <v>0.8604985405255134</v>
+        <v>-0.2352077730131438</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>-0.4793311925162053</v>
+      </c>
+      <c r="C9">
+        <v>0.9651162626818321</v>
+      </c>
+      <c r="D9">
+        <v>-0.4966564247754525</v>
+      </c>
+      <c r="E9">
+        <v>0.6210100253710626</v>
+      </c>
+      <c r="F9">
+        <v>-2.404685455798758</v>
+      </c>
+      <c r="G9">
+        <v>1.446023070766348</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/M6b_tourism_robustness_from_M4_regression_detail.xlsx
+++ b/outputs/M6b_tourism_robustness_from_M4_regression_detail.xlsx
@@ -52,7 +52,7 @@
     <t>xr_dep_pct</t>
   </si>
   <si>
-    <t>broad_money_pct_gdp</t>
+    <t>broad_money_growth_pct</t>
   </si>
   <si>
     <t>real_interest_rate_pct</t>
@@ -447,22 +447,22 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>23.55391278391144</v>
+        <v>-18.1643442936267</v>
       </c>
       <c r="C2">
-        <v>18.85268548824094</v>
+        <v>18.70324091359413</v>
       </c>
       <c r="D2">
-        <v>1.249366452254391</v>
+        <v>-0.9711869925401141</v>
       </c>
       <c r="E2">
-        <v>0.2157526692228244</v>
+        <v>0.3334934393759781</v>
       </c>
       <c r="F2">
-        <v>-14.05616569331358</v>
+        <v>-55.21186493767054</v>
       </c>
       <c r="G2">
-        <v>61.16399126113646</v>
+        <v>18.88317635041714</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -470,22 +470,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>-0.5806825349518495</v>
+        <v>0.07851225307961243</v>
       </c>
       <c r="C3">
-        <v>0.1331786876284242</v>
+        <v>0.1273568012047398</v>
       </c>
       <c r="D3">
-        <v>-4.360176130973639</v>
+        <v>0.6164747570363009</v>
       </c>
       <c r="E3">
-        <v>4.441200269100776E-05</v>
+        <v>0.5387996704600602</v>
       </c>
       <c r="F3">
-        <v>-0.8463667472261733</v>
+        <v>-0.1737570591529324</v>
       </c>
       <c r="G3">
-        <v>-0.3149983226775256</v>
+        <v>0.3307815653121572</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -493,22 +493,22 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>-0.03862170649776309</v>
+        <v>-0.01341572915012821</v>
       </c>
       <c r="C4">
-        <v>0.01379335142416218</v>
+        <v>0.01877705457740269</v>
       </c>
       <c r="D4">
-        <v>-2.800023381562543</v>
+        <v>-0.7144746315150737</v>
       </c>
       <c r="E4">
-        <v>0.006622196106624401</v>
+        <v>0.4763815211559486</v>
       </c>
       <c r="F4">
-        <v>-0.06613868968035831</v>
+        <v>-0.05060946045607784</v>
       </c>
       <c r="G4">
-        <v>-0.01110472331516787</v>
+        <v>0.02377800215582141</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -516,22 +516,22 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>-0.6570380213946319</v>
+        <v>1.260687746125777</v>
       </c>
       <c r="C5">
-        <v>1.702042261346384</v>
+        <v>0.5674503096873249</v>
       </c>
       <c r="D5">
-        <v>-0.3860292052177884</v>
+        <v>2.221670734166024</v>
       </c>
       <c r="E5">
-        <v>0.7006627693654872</v>
+        <v>0.02826318844984854</v>
       </c>
       <c r="F5">
-        <v>-4.052519426986354</v>
+        <v>0.1366778935162059</v>
       </c>
       <c r="G5">
-        <v>2.738443384197091</v>
+        <v>2.384697598735348</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -539,22 +539,22 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.1563052481550004</v>
+        <v>0.06370783450454984</v>
       </c>
       <c r="C6">
-        <v>0.06635874296351779</v>
+        <v>0.03680614160237153</v>
       </c>
       <c r="D6">
-        <v>2.355458243700197</v>
+        <v>1.730902282363793</v>
       </c>
       <c r="E6">
-        <v>0.02134841171578494</v>
+        <v>0.08615132091948663</v>
       </c>
       <c r="F6">
-        <v>0.02392317812765093</v>
+        <v>-0.009198048339014872</v>
       </c>
       <c r="G6">
-        <v>0.2886873181823499</v>
+        <v>0.1366137173481146</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -562,22 +562,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.0397526641451743</v>
+        <v>0.04464204399914826</v>
       </c>
       <c r="C7">
-        <v>0.05419130707645709</v>
+        <v>0.0394514579823844</v>
       </c>
       <c r="D7">
-        <v>0.7335616409674028</v>
+        <v>1.13156892754335</v>
       </c>
       <c r="E7">
-        <v>0.4657011376959139</v>
+        <v>0.2601698347484904</v>
       </c>
       <c r="F7">
-        <v>-0.06835603544567218</v>
+        <v>-0.03350370147845454</v>
       </c>
       <c r="G7">
-        <v>0.1478613637360208</v>
+        <v>0.122787789476751</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -585,22 +585,22 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>-0.6444652332392524</v>
+        <v>0.08357571721999686</v>
       </c>
       <c r="C8">
-        <v>0.2051471970746173</v>
+        <v>0.1127869836615656</v>
       </c>
       <c r="D8">
-        <v>-3.141477156058067</v>
+        <v>0.7410049857417808</v>
       </c>
       <c r="E8">
-        <v>0.00247621923669894</v>
+        <v>0.4602008291393611</v>
       </c>
       <c r="F8">
-        <v>-1.053722693465361</v>
+        <v>-0.1398335905510553</v>
       </c>
       <c r="G8">
-        <v>-0.2352077730131438</v>
+        <v>0.306985024991049</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -608,22 +608,22 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>-0.4793311925162053</v>
+        <v>-0.5473853365039651</v>
       </c>
       <c r="C9">
-        <v>0.9651162626818321</v>
+        <v>0.6736387261519013</v>
       </c>
       <c r="D9">
-        <v>-0.4966564247754525</v>
+        <v>-0.8125799709153496</v>
       </c>
       <c r="E9">
-        <v>0.6210100253710626</v>
+        <v>0.4181378933528914</v>
       </c>
       <c r="F9">
-        <v>-2.404685455798758</v>
+        <v>-1.881734005220554</v>
       </c>
       <c r="G9">
-        <v>1.446023070766348</v>
+        <v>0.7869633322126235</v>
       </c>
     </row>
   </sheetData>
